--- a/data/secondary2/secondary_quote_2026-07-22.xlsx
+++ b/data/secondary2/secondary_quote_2026-07-22.xlsx
@@ -13,42 +13,687 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
-  <si>
-    <t>暂无数据</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="227">
+  <si>
+    <t>债券简称</t>
+  </si>
+  <si>
+    <t>债券代码</t>
+  </si>
+  <si>
+    <t>剩余期限</t>
+  </si>
+  <si>
+    <t>最新成交</t>
+  </si>
+  <si>
+    <t>开盘</t>
+  </si>
+  <si>
+    <t>最高</t>
+  </si>
+  <si>
+    <t>最低</t>
+  </si>
+  <si>
+    <t>平均成交</t>
+  </si>
+  <si>
+    <t>前收</t>
+  </si>
+  <si>
+    <t>涨跌bp</t>
+  </si>
+  <si>
+    <t>成交笔数</t>
+  </si>
+  <si>
+    <t>GVN笔数</t>
+  </si>
+  <si>
+    <t>TKN笔数</t>
+  </si>
+  <si>
+    <t>中债(行/到)</t>
+  </si>
+  <si>
+    <t>中债偏离(BP)</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>流动性评分</t>
+  </si>
+  <si>
+    <t>中债隐含评级</t>
+  </si>
+  <si>
+    <t>中证净价</t>
+  </si>
+  <si>
+    <t>主承销商</t>
+  </si>
+  <si>
+    <t>成交偏离(BP)</t>
+  </si>
+  <si>
+    <t>发行日</t>
+  </si>
+  <si>
+    <t>主/债</t>
+  </si>
+  <si>
+    <t>24云能投MTN018</t>
+  </si>
+  <si>
+    <t>102483483.IB</t>
+  </si>
+  <si>
+    <t>13.06Y</t>
+  </si>
+  <si>
+    <t>3.3400</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>3.3271</t>
+  </si>
+  <si>
+    <t>1.29</t>
+  </si>
+  <si>
+    <t>10:06:45</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>96.1639</t>
+  </si>
+  <si>
+    <t>中国建设银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>AAA/--</t>
+  </si>
+  <si>
+    <t>25泸租01</t>
+  </si>
+  <si>
+    <t>257538.SH</t>
+  </si>
+  <si>
+    <t>1.66Y+2.00Y</t>
+  </si>
+  <si>
+    <t>2.5000</t>
+  </si>
+  <si>
+    <t>2.4842/2.7796</t>
+  </si>
+  <si>
+    <t>1.58</t>
+  </si>
+  <si>
+    <t>08:59:32</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>100.8864</t>
+  </si>
+  <si>
+    <t>浙商证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-10.74</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
+    <t>--/--</t>
+  </si>
+  <si>
+    <t>24利民V1</t>
+  </si>
+  <si>
+    <t>134124.SZ</t>
+  </si>
+  <si>
+    <t>1.41Y+4.00Y</t>
+  </si>
+  <si>
+    <t>2.3900</t>
+  </si>
+  <si>
+    <t>2.4449/3.0305</t>
+  </si>
+  <si>
+    <t>-5.49</t>
+  </si>
+  <si>
+    <t>01:32:00</t>
+  </si>
+  <si>
+    <t>100.8054</t>
+  </si>
+  <si>
+    <t>天风证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-0.92</t>
+  </si>
+  <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>AA+/--</t>
+  </si>
+  <si>
+    <t>25日发01</t>
+  </si>
+  <si>
+    <t>258555.SH</t>
+  </si>
+  <si>
+    <t>1.81Y+2.00Y</t>
+  </si>
+  <si>
+    <t>2.1400</t>
+  </si>
+  <si>
+    <t>2.1863/2.4586</t>
+  </si>
+  <si>
+    <t>-4.63</t>
+  </si>
+  <si>
+    <t>02:37:24</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>101.2115</t>
+  </si>
+  <si>
+    <t>国泰海通证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-4.22</t>
+  </si>
+  <si>
+    <t>2025-05-08</t>
+  </si>
+  <si>
+    <t>25北部湾银行二级资本债01</t>
+  </si>
+  <si>
+    <t>232580011.IB</t>
+  </si>
+  <si>
+    <t>3.84Y+5.00Y</t>
+  </si>
+  <si>
+    <t>2.1100</t>
+  </si>
+  <si>
+    <t>2.1200</t>
+  </si>
+  <si>
+    <t>-1.00</t>
+  </si>
+  <si>
+    <t>2.1322/2.7622</t>
+  </si>
+  <si>
+    <t>-2.22</t>
+  </si>
+  <si>
+    <t>07:06:50</t>
+  </si>
+  <si>
+    <t>103.0448</t>
+  </si>
+  <si>
+    <t>中国国际金融股份有限公司</t>
+  </si>
+  <si>
+    <t>2025-05-21</t>
+  </si>
+  <si>
+    <t>AAA/AA+</t>
+  </si>
+  <si>
+    <t>25株城08</t>
+  </si>
+  <si>
+    <t>259335.SH</t>
+  </si>
+  <si>
+    <t>3.99Y</t>
+  </si>
+  <si>
+    <t>2.0500</t>
+  </si>
+  <si>
+    <t>2.0537</t>
+  </si>
+  <si>
+    <t>-0.37</t>
+  </si>
+  <si>
+    <t>03:23:26</t>
+  </si>
+  <si>
+    <t>101.4877</t>
+  </si>
+  <si>
+    <t>财达证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-0.59</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>21安工01</t>
+  </si>
+  <si>
+    <t>197523.SH</t>
+  </si>
+  <si>
+    <t>109D</t>
+  </si>
+  <si>
+    <t>1.9500</t>
+  </si>
+  <si>
+    <t>1.9800</t>
+  </si>
+  <si>
+    <t>-3.00</t>
+  </si>
+  <si>
+    <t>1.9686</t>
+  </si>
+  <si>
+    <t>-1.86</t>
+  </si>
+  <si>
+    <t>09:24:20</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>101.0509</t>
+  </si>
+  <si>
+    <t>国联民生证券承销保荐有限公司</t>
+  </si>
+  <si>
+    <t>-1.42</t>
+  </si>
+  <si>
+    <t>2021-11-04</t>
+  </si>
+  <si>
+    <t>AA/AAA</t>
+  </si>
+  <si>
+    <t>25津金03</t>
+  </si>
+  <si>
+    <t>134275.SZ</t>
+  </si>
+  <si>
+    <t>1.85Y</t>
+  </si>
+  <si>
+    <t>1.9000</t>
+  </si>
+  <si>
+    <t>1.9121</t>
+  </si>
+  <si>
+    <t>-1.21</t>
+  </si>
+  <si>
+    <t>08:40:55</t>
+  </si>
+  <si>
+    <t>101.4581</t>
+  </si>
+  <si>
+    <t>国投证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-1.52</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>21彭水债</t>
+  </si>
+  <si>
+    <t>152808.SH</t>
+  </si>
+  <si>
+    <t>1.71Y</t>
+  </si>
+  <si>
+    <t>1.8500</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1.9055</t>
+  </si>
+  <si>
+    <t>-5.55</t>
+  </si>
+  <si>
+    <t>07:10:56</t>
+  </si>
+  <si>
+    <t>42.0803</t>
+  </si>
+  <si>
+    <t>兴业证券股份有限公司</t>
+  </si>
+  <si>
+    <t>-4.69</t>
+  </si>
+  <si>
+    <t>2021-04-05</t>
+  </si>
+  <si>
+    <t>22邛旅01</t>
+  </si>
+  <si>
+    <t>184384.SH</t>
+  </si>
+  <si>
+    <t>1.08Y</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1.9946</t>
+  </si>
+  <si>
+    <t>-14.46</t>
+  </si>
+  <si>
+    <t>05:58:36</t>
+  </si>
+  <si>
+    <t>50.7230</t>
+  </si>
+  <si>
+    <t>江海证券有限公司</t>
+  </si>
+  <si>
+    <t>-9.12</t>
+  </si>
+  <si>
+    <t>2022-08-17</t>
+  </si>
+  <si>
+    <t>26农行TLAC非资本债01B(BC)</t>
+  </si>
+  <si>
+    <t>312610002.IB</t>
+  </si>
+  <si>
+    <t>4.73Y+1.00Y</t>
+  </si>
+  <si>
+    <t>1.8300</t>
+  </si>
+  <si>
+    <t>1.8325</t>
+  </si>
+  <si>
+    <t>1.8319</t>
+  </si>
+  <si>
+    <t>1.8375</t>
+  </si>
+  <si>
+    <t>-0.75</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1.8361/1.8815</t>
+  </si>
+  <si>
+    <t>-0.61</t>
+  </si>
+  <si>
+    <t>08:31:03</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>100.9105</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>AAA/AAA</t>
+  </si>
+  <si>
+    <t>25农行二级资本债01A(BC)</t>
+  </si>
+  <si>
+    <t>232580016.IB</t>
+  </si>
+  <si>
+    <t>3.90Y+5.00Y</t>
+  </si>
+  <si>
+    <t>1.7350</t>
+  </si>
+  <si>
+    <t>1.7450</t>
+  </si>
+  <si>
+    <t>1.7425</t>
+  </si>
+  <si>
+    <t>1.7400</t>
+  </si>
+  <si>
+    <t>-0.50</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1.7457/2.1400</t>
+  </si>
+  <si>
+    <t>-1.07</t>
+  </si>
+  <si>
+    <t>07:47:13</t>
+  </si>
+  <si>
+    <t>101.7728</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>25衡阳城投PPN005</t>
+  </si>
+  <si>
+    <t>032580428.IB</t>
+  </si>
+  <si>
+    <t>1.93Y+2.00Y</t>
+  </si>
+  <si>
+    <t>1.7300</t>
+  </si>
+  <si>
+    <t>1.7436/1.9582</t>
+  </si>
+  <si>
+    <t>-1.36</t>
+  </si>
+  <si>
+    <t>05:59:05</t>
+  </si>
+  <si>
+    <t>100.8977</t>
+  </si>
+  <si>
+    <t>国信证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>25中信银行小微债</t>
+  </si>
+  <si>
+    <t>2528006.IB</t>
+  </si>
+  <si>
+    <t>1.68Y</t>
+  </si>
+  <si>
+    <t>1.5000</t>
+  </si>
+  <si>
+    <t>1.5050</t>
+  </si>
+  <si>
+    <t>1.5013</t>
+  </si>
+  <si>
+    <t>-0.13</t>
+  </si>
+  <si>
+    <t>07:07:52</t>
+  </si>
+  <si>
+    <t>100.6983</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
   </si>
   <si>
     <t>成交日期</t>
   </si>
   <si>
-    <t>债券简称</t>
-  </si>
-  <si>
-    <t>剩余期限</t>
-  </si>
-  <si>
-    <t>最新成交</t>
-  </si>
-  <si>
     <t>中债/中证</t>
   </si>
   <si>
-    <t>中债偏离(BP)</t>
-  </si>
-  <si>
     <t>发行人</t>
   </si>
   <si>
     <t>区域</t>
   </si>
   <si>
-    <t>债券代码</t>
-  </si>
-  <si>
-    <t>中债隐含评级</t>
-  </si>
-  <si>
-    <t>主/债</t>
+    <t>2026-7-22</t>
+  </si>
+  <si>
+    <t>云南省能源集团有限公司</t>
+  </si>
+  <si>
+    <t>云南</t>
+  </si>
+  <si>
+    <t>泸州发展融资租赁有限公司</t>
+  </si>
+  <si>
+    <t>四川</t>
+  </si>
+  <si>
+    <t>邹城市利民产业集团有限公司</t>
+  </si>
+  <si>
+    <t>山东</t>
+  </si>
+  <si>
+    <t>日照农发集团有限公司市政</t>
+  </si>
+  <si>
+    <t>广西北部湾银行股份有限公司</t>
+  </si>
+  <si>
+    <t>广西</t>
+  </si>
+  <si>
+    <t>株洲市城市建设发展集团有限公司</t>
+  </si>
+  <si>
+    <t>湖南</t>
+  </si>
+  <si>
+    <t>安顺市工业投资股份有限公司</t>
+  </si>
+  <si>
+    <t>贵州</t>
+  </si>
+  <si>
+    <t>天津新金融投资有限责任公司</t>
+  </si>
+  <si>
+    <t>天津</t>
+  </si>
+  <si>
+    <t>彭水县城市建设投资有限责任公司</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
+    <t>邛崃市天际山水文化旅游投资集团有限公司</t>
+  </si>
+  <si>
+    <t>中国农业银行股份有限公司</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>衡阳市城市建设投资有限公司</t>
+  </si>
+  <si>
+    <t>中信银行股份有限公司</t>
   </si>
 </sst>
 </file>
@@ -425,15 +1070,1088 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="30" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" t="s">
+        <v>59</v>
+      </c>
+      <c r="T4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" t="s">
+        <v>62</v>
+      </c>
+      <c r="W4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>71</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s">
+        <v>73</v>
+      </c>
+      <c r="U5" t="s">
+        <v>74</v>
+      </c>
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" t="s">
+        <v>86</v>
+      </c>
+      <c r="U6" t="s">
+        <v>83</v>
+      </c>
+      <c r="V6" t="s">
+        <v>87</v>
+      </c>
+      <c r="W6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" t="s">
+        <v>94</v>
+      </c>
+      <c r="P7" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R7" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" t="s">
+        <v>96</v>
+      </c>
+      <c r="T7" t="s">
+        <v>97</v>
+      </c>
+      <c r="U7" t="s">
+        <v>98</v>
+      </c>
+      <c r="V7" t="s">
+        <v>99</v>
+      </c>
+      <c r="W7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" t="s">
+        <v>106</v>
+      </c>
+      <c r="O8" t="s">
+        <v>107</v>
+      </c>
+      <c r="P8" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>109</v>
+      </c>
+      <c r="R8" t="s">
+        <v>34</v>
+      </c>
+      <c r="S8" t="s">
+        <v>110</v>
+      </c>
+      <c r="T8" t="s">
+        <v>111</v>
+      </c>
+      <c r="U8" t="s">
+        <v>112</v>
+      </c>
+      <c r="V8" t="s">
+        <v>113</v>
+      </c>
+      <c r="W8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O9" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" t="s">
+        <v>122</v>
+      </c>
+      <c r="T9" t="s">
+        <v>123</v>
+      </c>
+      <c r="U9" t="s">
+        <v>124</v>
+      </c>
+      <c r="V9" t="s">
+        <v>125</v>
+      </c>
+      <c r="W9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s">
+        <v>130</v>
+      </c>
+      <c r="N10" t="s">
+        <v>131</v>
+      </c>
+      <c r="O10" t="s">
+        <v>132</v>
+      </c>
+      <c r="P10" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>109</v>
+      </c>
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
+        <v>134</v>
+      </c>
+      <c r="T10" t="s">
+        <v>135</v>
+      </c>
+      <c r="U10" t="s">
+        <v>136</v>
+      </c>
+      <c r="V10" t="s">
+        <v>137</v>
+      </c>
+      <c r="W10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>141</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>141</v>
+      </c>
+      <c r="N11" t="s">
+        <v>142</v>
+      </c>
+      <c r="O11" t="s">
+        <v>143</v>
+      </c>
+      <c r="P11" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" t="s">
+        <v>145</v>
+      </c>
+      <c r="T11" t="s">
+        <v>146</v>
+      </c>
+      <c r="U11" t="s">
+        <v>147</v>
+      </c>
+      <c r="V11" t="s">
+        <v>148</v>
+      </c>
+      <c r="W11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" t="s">
+        <v>156</v>
+      </c>
+      <c r="K12" t="s">
+        <v>157</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>157</v>
+      </c>
+      <c r="N12" t="s">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s">
+        <v>159</v>
+      </c>
+      <c r="P12" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>161</v>
+      </c>
+      <c r="R12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" t="s">
+        <v>162</v>
+      </c>
+      <c r="T12" t="s">
+        <v>86</v>
+      </c>
+      <c r="U12" t="s">
+        <v>159</v>
+      </c>
+      <c r="V12" t="s">
+        <v>163</v>
+      </c>
+      <c r="W12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G13" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" t="s">
+        <v>171</v>
+      </c>
+      <c r="J13" t="s">
+        <v>172</v>
+      </c>
+      <c r="K13" t="s">
+        <v>173</v>
+      </c>
+      <c r="L13" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" t="s">
+        <v>174</v>
+      </c>
+      <c r="N13" t="s">
+        <v>175</v>
+      </c>
+      <c r="O13" t="s">
+        <v>176</v>
+      </c>
+      <c r="P13" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>161</v>
+      </c>
+      <c r="R13" t="s">
+        <v>34</v>
+      </c>
+      <c r="S13" t="s">
+        <v>178</v>
+      </c>
+      <c r="T13" t="s">
+        <v>86</v>
+      </c>
+      <c r="U13" t="s">
+        <v>176</v>
+      </c>
+      <c r="V13" t="s">
+        <v>179</v>
+      </c>
+      <c r="W13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" t="s">
+        <v>183</v>
+      </c>
+      <c r="I14" t="s">
+        <v>171</v>
+      </c>
+      <c r="J14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" t="s">
+        <v>184</v>
+      </c>
+      <c r="O14" t="s">
+        <v>185</v>
+      </c>
+      <c r="P14" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>109</v>
+      </c>
+      <c r="R14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S14" t="s">
+        <v>187</v>
+      </c>
+      <c r="T14" t="s">
+        <v>188</v>
+      </c>
+      <c r="U14" t="s">
+        <v>185</v>
+      </c>
+      <c r="V14" t="s">
+        <v>189</v>
+      </c>
+      <c r="W14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" t="s">
+        <v>193</v>
+      </c>
+      <c r="H15" t="s">
+        <v>193</v>
+      </c>
+      <c r="I15" t="s">
+        <v>194</v>
+      </c>
+      <c r="J15" t="s">
+        <v>172</v>
+      </c>
+      <c r="K15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" t="s">
+        <v>195</v>
+      </c>
+      <c r="O15" t="s">
+        <v>196</v>
+      </c>
+      <c r="P15" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>71</v>
+      </c>
+      <c r="R15" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" t="s">
+        <v>198</v>
+      </c>
+      <c r="T15" t="s">
+        <v>86</v>
+      </c>
+      <c r="U15" t="s">
+        <v>196</v>
+      </c>
+      <c r="V15" t="s">
+        <v>199</v>
+      </c>
+      <c r="W15" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -444,50 +2162,544 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" t="s">
+        <v>216</v>
+      </c>
+      <c r="H8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" t="s">
+        <v>220</v>
+      </c>
+      <c r="H10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11" t="s">
+        <v>208</v>
+      </c>
+      <c r="I11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" t="s">
+        <v>223</v>
+      </c>
+      <c r="H13" t="s">
+        <v>224</v>
+      </c>
+      <c r="I13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" t="s">
+        <v>181</v>
+      </c>
+      <c r="J14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" t="s">
+        <v>226</v>
+      </c>
+      <c r="H15" t="s">
+        <v>224</v>
+      </c>
+      <c r="I15" t="s">
+        <v>191</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -498,50 +2710,544 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" t="s">
+        <v>216</v>
+      </c>
+      <c r="H8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" t="s">
+        <v>220</v>
+      </c>
+      <c r="H10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11" t="s">
+        <v>208</v>
+      </c>
+      <c r="I11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" t="s">
+        <v>223</v>
+      </c>
+      <c r="H13" t="s">
+        <v>224</v>
+      </c>
+      <c r="I13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" t="s">
+        <v>215</v>
+      </c>
+      <c r="I14" t="s">
+        <v>181</v>
+      </c>
+      <c r="J14" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" t="s">
+        <v>226</v>
+      </c>
+      <c r="H15" t="s">
+        <v>224</v>
+      </c>
+      <c r="I15" t="s">
+        <v>191</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
